--- a/VerveStacks_ZAF_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_ZAF_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ZAF_grids_kan\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{80FD0A09-9A1F-44D3-AD89-46C7A733195A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{60046164-7AFB-4DB0-A87E-0D12FA9CC862}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2573" yWindow="2573" windowWidth="21600" windowHeight="12682" xr2:uid="{4A1F17F4-E4B1-419F-A029-D17CCAF9BA38}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{64750327-C800-46D6-A452-47025E923DEE}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -1804,7 +1804,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CDC77B7-EB36-4C01-BF6D-28160C45BD1C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF9FCED2-F70E-4170-BBA5-FA8B1A1824D1}">
   <dimension ref="B3:L186"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ZAF_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_ZAF_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ZAF_grids_kan\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{60046164-7AFB-4DB0-A87E-0D12FA9CC862}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{958EA3F0-287D-4B34-8400-8B7DB36FE2D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{64750327-C800-46D6-A452-47025E923DEE}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{60B8D298-0501-4EAB-905D-5352643D375B}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -1804,7 +1804,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF9FCED2-F70E-4170-BBA5-FA8B1A1824D1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8851220D-E65E-4135-81BA-1326686468C5}">
   <dimension ref="B3:L186"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ZAF_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_ZAF_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ZAF_grids_kan\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{958EA3F0-287D-4B34-8400-8B7DB36FE2D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D1EDB29C-9E48-4488-AA3B-ED460DD88E76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{60B8D298-0501-4EAB-905D-5352643D375B}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{1C6FC377-62B2-4E66-A4BC-664F1743D930}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -1804,7 +1804,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8851220D-E65E-4135-81BA-1326686468C5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D7269B6-F3DA-4019-BB78-37247926BE14}">
   <dimension ref="B3:L186"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ZAF_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_ZAF_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ZAF_grids_kan\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D1EDB29C-9E48-4488-AA3B-ED460DD88E76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2F400CFE-FBAF-45A0-82F2-EDEC77A155E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{1C6FC377-62B2-4E66-A4BC-664F1743D930}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{C75B7F9D-5AB2-4223-87C5-D1E1EA2AC3ED}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -31,6 +31,9 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="2"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
@@ -68,943 +71,943 @@
     <t>ELC</t>
   </si>
   <si>
-    <t>e_ZA1-400</t>
-  </si>
-  <si>
-    <t>e_w182408147-400</t>
-  </si>
-  <si>
-    <t>g_ZA1-400-w182408147-400</t>
+    <t>e_ZA1-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w182408147-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_ZA1-400_ZAF-w182408147-400_ZAF</t>
   </si>
   <si>
     <t>B</t>
   </si>
   <si>
-    <t>e_ZA11-400</t>
-  </si>
-  <si>
-    <t>e_w220129604-400</t>
-  </si>
-  <si>
-    <t>g_ZA11-400-w220129604-400</t>
-  </si>
-  <si>
-    <t>e_ZA15-400</t>
-  </si>
-  <si>
-    <t>e_ZA18-400</t>
-  </si>
-  <si>
-    <t>g_ZA15-400-ZA18-400</t>
-  </si>
-  <si>
-    <t>e_ZA16-400</t>
-  </si>
-  <si>
-    <t>g_ZA18-400-ZA16-400</t>
-  </si>
-  <si>
-    <t>e_ZA2-400</t>
-  </si>
-  <si>
-    <t>e_w685294883-400</t>
-  </si>
-  <si>
-    <t>g_ZA2-400-w685294883-400</t>
-  </si>
-  <si>
-    <t>e_ZA20-400</t>
-  </si>
-  <si>
-    <t>g_ZA20-400-w220129604-400</t>
-  </si>
-  <si>
-    <t>e_ZA22-400</t>
-  </si>
-  <si>
-    <t>e_w209976655-400</t>
-  </si>
-  <si>
-    <t>g_ZA22-400-w209976655-400</t>
-  </si>
-  <si>
-    <t>e_ZA24-400</t>
-  </si>
-  <si>
-    <t>e_w98231311-400</t>
-  </si>
-  <si>
-    <t>g_ZA24-400-w98231311-400</t>
-  </si>
-  <si>
-    <t>e_ZA25-400</t>
-  </si>
-  <si>
-    <t>e_w125769921-400</t>
-  </si>
-  <si>
-    <t>g_ZA25-400-w125769921-400</t>
-  </si>
-  <si>
-    <t>e_ZA26-400</t>
-  </si>
-  <si>
-    <t>e_w127585817-400</t>
-  </si>
-  <si>
-    <t>g_ZA26-400-w127585817-400</t>
-  </si>
-  <si>
-    <t>e_w213181313-400</t>
-  </si>
-  <si>
-    <t>g_ZA26-400-w213181313-400</t>
-  </si>
-  <si>
-    <t>e_ZA29-400</t>
-  </si>
-  <si>
-    <t>g_ZA29-400-w127585817-400</t>
-  </si>
-  <si>
-    <t>e_ZA3-400</t>
-  </si>
-  <si>
-    <t>e_w200232961-400</t>
-  </si>
-  <si>
-    <t>g_ZA3-400-w200232961-400</t>
-  </si>
-  <si>
-    <t>e_ZA30-400</t>
-  </si>
-  <si>
-    <t>g_ZA30-400-ZA29-400</t>
-  </si>
-  <si>
-    <t>e_w181284049-400</t>
-  </si>
-  <si>
-    <t>g_ZA30-400-w181284049-400</t>
-  </si>
-  <si>
-    <t>e_ZA31-400</t>
-  </si>
-  <si>
-    <t>e_w176362710-400</t>
-  </si>
-  <si>
-    <t>g_ZA31-400-w176362710-400</t>
-  </si>
-  <si>
-    <t>e_ZA36-400</t>
-  </si>
-  <si>
-    <t>g_ZA36-400-w176362710-400</t>
-  </si>
-  <si>
-    <t>e_ZA39-400</t>
-  </si>
-  <si>
-    <t>e_w586032034-400</t>
-  </si>
-  <si>
-    <t>g_ZA39-400-w586032034-400</t>
-  </si>
-  <si>
-    <t>e_ZA40-400</t>
-  </si>
-  <si>
-    <t>e_w182042518-400</t>
-  </si>
-  <si>
-    <t>g_ZA40-400-w182042518-400</t>
-  </si>
-  <si>
-    <t>e_ZA5-400</t>
-  </si>
-  <si>
-    <t>e_ZA4-400</t>
-  </si>
-  <si>
-    <t>g_ZA5-400-ZA4-400</t>
-  </si>
-  <si>
-    <t>e_ZA6-400</t>
-  </si>
-  <si>
-    <t>g_ZA6-400-ZA5-400</t>
-  </si>
-  <si>
-    <t>e_r17287657-400</t>
-  </si>
-  <si>
-    <t>e_w631673098-400</t>
-  </si>
-  <si>
-    <t>g_r17287657-400-w631673098-400</t>
-  </si>
-  <si>
-    <t>e_w102682082-400</t>
-  </si>
-  <si>
-    <t>e_w177800991-400</t>
-  </si>
-  <si>
-    <t>g_w102682082-400-w177800991-400</t>
-  </si>
-  <si>
-    <t>e_w102925909-400</t>
-  </si>
-  <si>
-    <t>g_w102925909-400-w98231311-400</t>
-  </si>
-  <si>
-    <t>e_w103079596-400</t>
-  </si>
-  <si>
-    <t>e_w167540668-400</t>
-  </si>
-  <si>
-    <t>g_w103079596-400-w167540668-400</t>
-  </si>
-  <si>
-    <t>e_w87404898-400</t>
-  </si>
-  <si>
-    <t>g_w103079596-400-w87404898-400</t>
-  </si>
-  <si>
-    <t>e_w104080393-400</t>
-  </si>
-  <si>
-    <t>e_w183759046-400</t>
-  </si>
-  <si>
-    <t>g_w104080393-400-w183759046-400</t>
-  </si>
-  <si>
-    <t>e_w238322344-400</t>
-  </si>
-  <si>
-    <t>g_w104080393-400-w238322344-400</t>
-  </si>
-  <si>
-    <t>e_w105759402-400</t>
-  </si>
-  <si>
-    <t>g_w105759402-400-w127585817-400</t>
-  </si>
-  <si>
-    <t>e_w167648085-400</t>
-  </si>
-  <si>
-    <t>g_w105759402-400-w167648085-400</t>
-  </si>
-  <si>
-    <t>e_w105811523-400</t>
-  </si>
-  <si>
-    <t>e_w65600948-400</t>
-  </si>
-  <si>
-    <t>g_w105811523-400-w65600948-400</t>
-  </si>
-  <si>
-    <t>g_w105811523-400-w98231311-400</t>
-  </si>
-  <si>
-    <t>e_w107431792-400</t>
-  </si>
-  <si>
-    <t>g_w107431792-400-ZA40-400</t>
-  </si>
-  <si>
-    <t>e_w193978748-400</t>
-  </si>
-  <si>
-    <t>g_w107431792-400-w193978748-400</t>
-  </si>
-  <si>
-    <t>e_w107937167-400</t>
-  </si>
-  <si>
-    <t>g_w107937167-400-r17287657-400</t>
-  </si>
-  <si>
-    <t>e_w1146812331-400</t>
-  </si>
-  <si>
-    <t>e_w1146878078-400</t>
-  </si>
-  <si>
-    <t>g_w1146812331-400-w1146878078-400</t>
-  </si>
-  <si>
-    <t>e_w120584910-400</t>
-  </si>
-  <si>
-    <t>e_w545652232-400</t>
-  </si>
-  <si>
-    <t>g_w120584910-400-w545652232-400</t>
-  </si>
-  <si>
-    <t>e_w62191005-400</t>
-  </si>
-  <si>
-    <t>g_w120584910-400-w62191005-400</t>
-  </si>
-  <si>
-    <t>e_w120941269-400</t>
-  </si>
-  <si>
-    <t>e_w131625968-400</t>
-  </si>
-  <si>
-    <t>g_w120941269-400-w131625968-400</t>
-  </si>
-  <si>
-    <t>e_w125754107-400</t>
-  </si>
-  <si>
-    <t>g_w125754107-400-w125769921-400</t>
-  </si>
-  <si>
-    <t>e_w183402339-400</t>
-  </si>
-  <si>
-    <t>g_w125769921-400-w183402339-400</t>
-  </si>
-  <si>
-    <t>e_w663042849-400</t>
-  </si>
-  <si>
-    <t>g_w125769921-400-w663042849-400</t>
-  </si>
-  <si>
-    <t>g_w127585817-400-ZA30-400</t>
-  </si>
-  <si>
-    <t>e_ZA33-400</t>
-  </si>
-  <si>
-    <t>g_w127585817-400-ZA33-400</t>
-  </si>
-  <si>
-    <t>g_w127585817-400-w176362710-400</t>
-  </si>
-  <si>
-    <t>e_w142414070-400</t>
-  </si>
-  <si>
-    <t>e_w181366662-400</t>
-  </si>
-  <si>
-    <t>g_w142414070-400-w181366662-400</t>
-  </si>
-  <si>
-    <t>e_w89637370-400</t>
-  </si>
-  <si>
-    <t>g_w142414070-400-w89637370-400</t>
-  </si>
-  <si>
-    <t>e_w92348290-400</t>
-  </si>
-  <si>
-    <t>g_w142414070-400-w92348290-400</t>
-  </si>
-  <si>
-    <t>e_w142414070-765</t>
-  </si>
-  <si>
-    <t>e_ZA38-765</t>
-  </si>
-  <si>
-    <t>g_w142414070-765-ZA38-765</t>
-  </si>
-  <si>
-    <t>e_w181366662-765</t>
-  </si>
-  <si>
-    <t>g_w142414070-765-w181366662-765</t>
-  </si>
-  <si>
-    <t>e_w156418705-400</t>
-  </si>
-  <si>
-    <t>e_w184552955-400</t>
-  </si>
-  <si>
-    <t>g_w156418705-400-w184552955-400</t>
-  </si>
-  <si>
-    <t>e_w162871098-400</t>
-  </si>
-  <si>
-    <t>g_w162871098-400-w125769921-400</t>
-  </si>
-  <si>
-    <t>e_w87434264-400</t>
-  </si>
-  <si>
-    <t>g_w167540668-400-w87434264-400</t>
-  </si>
-  <si>
-    <t>e_w167540668-765</t>
-  </si>
-  <si>
-    <t>e_w178968761-765</t>
-  </si>
-  <si>
-    <t>g_w167540668-765-w178968761-765</t>
-  </si>
-  <si>
-    <t>e_w167590549-400</t>
-  </si>
-  <si>
-    <t>g_w167590549-400-w142414070-400</t>
-  </si>
-  <si>
-    <t>g_w167590549-400-w177800991-400</t>
-  </si>
-  <si>
-    <t>g_w167590549-400-w62191005-400</t>
-  </si>
-  <si>
-    <t>e_w89173873-400</t>
-  </si>
-  <si>
-    <t>g_w167590549-400-w89173873-400</t>
-  </si>
-  <si>
-    <t>g_w167648085-400-w120941269-400</t>
-  </si>
-  <si>
-    <t>g_w167648085-400-w181284049-400</t>
-  </si>
-  <si>
-    <t>e_w219596295-400</t>
-  </si>
-  <si>
-    <t>g_w167648085-400-w219596295-400</t>
-  </si>
-  <si>
-    <t>e_w169647963-400</t>
-  </si>
-  <si>
-    <t>g_w169647963-400-w89637370-400</t>
-  </si>
-  <si>
-    <t>e_w170672051-400</t>
-  </si>
-  <si>
-    <t>g_w170672051-400-ZA15-400</t>
-  </si>
-  <si>
-    <t>e_w185171518-400</t>
-  </si>
-  <si>
-    <t>g_w170672051-400-w185171518-400</t>
-  </si>
-  <si>
-    <t>g_w170672051-400-w209976655-400</t>
-  </si>
-  <si>
-    <t>g_w170672051-400-w220129604-400</t>
-  </si>
-  <si>
-    <t>e_w107391770-400</t>
-  </si>
-  <si>
-    <t>g_w176362710-400-w107391770-400</t>
-  </si>
-  <si>
-    <t>e_w207991752-400</t>
-  </si>
-  <si>
-    <t>g_w176362710-400-w207991752-400</t>
-  </si>
-  <si>
-    <t>e_w176940672-400</t>
-  </si>
-  <si>
-    <t>e_w184581460-400</t>
-  </si>
-  <si>
-    <t>g_w176940672-400-w184581460-400</t>
-  </si>
-  <si>
-    <t>e_w934819484-400</t>
-  </si>
-  <si>
-    <t>g_w177800991-400-w934819484-400</t>
-  </si>
-  <si>
-    <t>e_w178240552-400</t>
-  </si>
-  <si>
-    <t>g_w178240552-400-w105811523-400</t>
-  </si>
-  <si>
-    <t>e_w178968761-400</t>
-  </si>
-  <si>
-    <t>g_w178968761-400-ZA22-400</t>
-  </si>
-  <si>
-    <t>e_w185497473-400</t>
-  </si>
-  <si>
-    <t>g_w178968761-400-w185497473-400</t>
-  </si>
-  <si>
-    <t>e_w209365700-400</t>
-  </si>
-  <si>
-    <t>g_w178968761-400-w209365700-400</t>
-  </si>
-  <si>
-    <t>g_w178968761-400-w238322344-400</t>
-  </si>
-  <si>
-    <t>g_w178968761-400-w65600948-400</t>
-  </si>
-  <si>
-    <t>e_w179136373-400</t>
-  </si>
-  <si>
-    <t>g_w179136373-400-w213181313-400</t>
-  </si>
-  <si>
-    <t>e_w179140081-400</t>
-  </si>
-  <si>
-    <t>g_w179140081-400-ZA22-400</t>
-  </si>
-  <si>
-    <t>g_w179140081-400-w178968761-400</t>
-  </si>
-  <si>
-    <t>g_w179140081-400-w209365700-400</t>
-  </si>
-  <si>
-    <t>g_w181284049-400-w107391770-400</t>
-  </si>
-  <si>
-    <t>g_w181366662-400-w107937167-400</t>
-  </si>
-  <si>
-    <t>g_w181366662-400-w92348290-400</t>
-  </si>
-  <si>
-    <t>e_w179136373-765</t>
-  </si>
-  <si>
-    <t>g_w181366662-765-w179136373-765</t>
-  </si>
-  <si>
-    <t>e_w219384657-400</t>
-  </si>
-  <si>
-    <t>g_w182042518-400-w219384657-400</t>
-  </si>
-  <si>
-    <t>g_w182408147-400-w184552955-400</t>
-  </si>
-  <si>
-    <t>g_w182408147-400-w685294883-400</t>
-  </si>
-  <si>
-    <t>g_w183402339-400-w142414070-400</t>
-  </si>
-  <si>
-    <t>e_w183757901-400</t>
-  </si>
-  <si>
-    <t>g_w183757901-400-w219596295-400</t>
-  </si>
-  <si>
-    <t>g_w183759046-400-w167648085-400</t>
-  </si>
-  <si>
-    <t>e_w184201271-400</t>
-  </si>
-  <si>
-    <t>g_w184201271-400-w176940672-400</t>
-  </si>
-  <si>
-    <t>g_w184201271-400-w200232961-400</t>
-  </si>
-  <si>
-    <t>g_w184552955-400-ZA6-400</t>
-  </si>
-  <si>
-    <t>e_w208749745-400</t>
-  </si>
-  <si>
-    <t>g_w184552955-400-w208749745-400</t>
-  </si>
-  <si>
-    <t>e_w184560833-400</t>
-  </si>
-  <si>
-    <t>e_ZA7-400</t>
-  </si>
-  <si>
-    <t>g_w184560833-400-ZA7-400</t>
-  </si>
-  <si>
-    <t>g_w184560833-400-w1146878078-400</t>
-  </si>
-  <si>
-    <t>e_w83525879-400</t>
-  </si>
-  <si>
-    <t>g_w184581460-400-w83525879-400</t>
-  </si>
-  <si>
-    <t>g_w185171518-400-ZA15-400</t>
-  </si>
-  <si>
-    <t>e_ZA17-400</t>
-  </si>
-  <si>
-    <t>g_w185171518-400-ZA17-400</t>
-  </si>
-  <si>
-    <t>g_w185171518-400-w1146878078-400</t>
-  </si>
-  <si>
-    <t>g_w185497473-400-w170672051-400</t>
-  </si>
-  <si>
-    <t>g_w185497473-400-w178968761-400</t>
-  </si>
-  <si>
-    <t>e_w193465369-400</t>
-  </si>
-  <si>
-    <t>g_w193465369-400-w193978748-400</t>
-  </si>
-  <si>
-    <t>e_w193977981-765</t>
-  </si>
-  <si>
-    <t>g_w193977981-765-w142414070-765</t>
-  </si>
-  <si>
-    <t>g_w193978748-400-w125754107-400</t>
-  </si>
-  <si>
-    <t>e_w200223220-400</t>
-  </si>
-  <si>
-    <t>g_w200223220-400-w98231311-400</t>
-  </si>
-  <si>
-    <t>g_w200232961-400-ZA2-400</t>
-  </si>
-  <si>
-    <t>g_w200232961-400-ZA3-400</t>
-  </si>
-  <si>
-    <t>e_w200757306-400</t>
-  </si>
-  <si>
-    <t>e_w496302277-400</t>
-  </si>
-  <si>
-    <t>g_w200757306-400-w496302277-400</t>
-  </si>
-  <si>
-    <t>g_w209365700-400-w167648085-400</t>
-  </si>
-  <si>
-    <t>g_w209365700-400-w179136373-400</t>
-  </si>
-  <si>
-    <t>g_w209365700-400-w213181313-400</t>
-  </si>
-  <si>
-    <t>g_w209365700-400-w238322344-400</t>
-  </si>
-  <si>
-    <t>g_w209976655-400-w220129604-400</t>
-  </si>
-  <si>
-    <t>e_w260486370-400</t>
-  </si>
-  <si>
-    <t>g_w209976655-400-w260486370-400</t>
-  </si>
-  <si>
-    <t>g_w213181313-400-ZA29-400</t>
-  </si>
-  <si>
-    <t>g_w213181313-400-w167648085-400</t>
-  </si>
-  <si>
-    <t>g_w213181313-400-w219596295-400</t>
-  </si>
-  <si>
-    <t>g_w219384657-400-w62191005-400</t>
-  </si>
-  <si>
-    <t>e_w219384657-765</t>
-  </si>
-  <si>
-    <t>e_w586032034-765</t>
-  </si>
-  <si>
-    <t>g_w219384657-765-w586032034-765</t>
-  </si>
-  <si>
-    <t>g_w219596295-400-w120941269-400</t>
-  </si>
-  <si>
-    <t>g_w219596295-400-w131625968-400</t>
-  </si>
-  <si>
-    <t>g_w220129604-400-w156418705-400</t>
-  </si>
-  <si>
-    <t>e_w230551819-400</t>
-  </si>
-  <si>
-    <t>g_w230551819-400-w176940672-400</t>
-  </si>
-  <si>
-    <t>g_w230551819-400-w182408147-400</t>
-  </si>
-  <si>
-    <t>g_w230551819-400-w184581460-400</t>
-  </si>
-  <si>
-    <t>g_w230551819-400-w200232961-400</t>
-  </si>
-  <si>
-    <t>e_ZA23-400</t>
-  </si>
-  <si>
-    <t>g_w238322344-400-ZA23-400</t>
-  </si>
-  <si>
-    <t>g_w238322344-400-w183757901-400</t>
-  </si>
-  <si>
-    <t>g_w238322344-400-w185171518-400</t>
-  </si>
-  <si>
-    <t>e_w359805008-400</t>
-  </si>
-  <si>
-    <t>g_w359805008-400-ZA18-400</t>
-  </si>
-  <si>
-    <t>e_w75136015-400</t>
-  </si>
-  <si>
-    <t>g_w359805008-400-w75136015-400</t>
-  </si>
-  <si>
-    <t>e_w455498147-400</t>
-  </si>
-  <si>
-    <t>g_w455498147-400-w83525879-400</t>
-  </si>
-  <si>
-    <t>g_w496302277-400-w167540668-400</t>
-  </si>
-  <si>
-    <t>g_w545652232-400-w102682082-400</t>
-  </si>
-  <si>
-    <t>g_w586032034-765-w193977981-765</t>
-  </si>
-  <si>
-    <t>g_w62191005-400-w177800991-400</t>
-  </si>
-  <si>
-    <t>e_w62193952-400</t>
-  </si>
-  <si>
-    <t>g_w62193952-400-w62191005-400</t>
-  </si>
-  <si>
-    <t>e_w62218063-400</t>
-  </si>
-  <si>
-    <t>g_w62218063-400-w62193952-400</t>
-  </si>
-  <si>
-    <t>g_w631673098-400-w207991752-400</t>
-  </si>
-  <si>
-    <t>g_w65600948-400-w185171518-400</t>
-  </si>
-  <si>
-    <t>g_w65600948-400-w98231311-400</t>
-  </si>
-  <si>
-    <t>e_w663042845-400</t>
-  </si>
-  <si>
-    <t>g_w663042845-400-w663042849-400</t>
-  </si>
-  <si>
-    <t>g_w663042849-400-w200757306-400</t>
-  </si>
-  <si>
-    <t>g_w685294883-400-ZA5-400</t>
-  </si>
-  <si>
-    <t>g_w685294883-400-w184552955-400</t>
-  </si>
-  <si>
-    <t>e_w693869805-400</t>
-  </si>
-  <si>
-    <t>g_w693869805-400-ZA3-400</t>
-  </si>
-  <si>
-    <t>g_w693869805-400-w182408147-400</t>
-  </si>
-  <si>
-    <t>g_w693869805-400-w184201271-400</t>
-  </si>
-  <si>
-    <t>g_w693869805-400-w87434264-400</t>
-  </si>
-  <si>
-    <t>g_w75136015-400-ZA18-400</t>
-  </si>
-  <si>
-    <t>g_w75136015-400-w185497473-400</t>
-  </si>
-  <si>
-    <t>g_w75136015-400-w455498147-400</t>
-  </si>
-  <si>
-    <t>g_w75136015-400-w83525879-400</t>
-  </si>
-  <si>
-    <t>e_ZA14-400</t>
-  </si>
-  <si>
-    <t>g_w83525879-400-ZA14-400</t>
-  </si>
-  <si>
-    <t>e_ZA19-400</t>
-  </si>
-  <si>
-    <t>g_w83525879-400-ZA19-400</t>
-  </si>
-  <si>
-    <t>g_w83525879-400-w170672051-400</t>
-  </si>
-  <si>
-    <t>g_w83525879-400-w185497473-400</t>
-  </si>
-  <si>
-    <t>e_w836844162-400</t>
-  </si>
-  <si>
-    <t>g_w836844162-400-ZA40-400</t>
-  </si>
-  <si>
-    <t>e_ZA41-400</t>
-  </si>
-  <si>
-    <t>g_w836844162-400-ZA41-400</t>
-  </si>
-  <si>
-    <t>e_ZA42-400</t>
-  </si>
-  <si>
-    <t>g_w836844162-400-ZA42-400</t>
-  </si>
-  <si>
-    <t>e_ZA43-400</t>
-  </si>
-  <si>
-    <t>g_w836844162-400-ZA43-400</t>
-  </si>
-  <si>
-    <t>e_ZA44-400</t>
-  </si>
-  <si>
-    <t>g_w836844162-400-ZA44-400</t>
-  </si>
-  <si>
-    <t>g_w87404898-400-w182408147-400</t>
-  </si>
-  <si>
-    <t>g_w87404898-400-w359805008-400</t>
-  </si>
-  <si>
-    <t>g_w87404898-400-w75136015-400</t>
-  </si>
-  <si>
-    <t>g_w87404898-400-w87434264-400</t>
-  </si>
-  <si>
-    <t>g_w87434264-400-w178240552-400</t>
-  </si>
-  <si>
-    <t>g_w89173873-400-w142414070-400</t>
-  </si>
-  <si>
-    <t>g_w89173873-400-w167590549-400</t>
-  </si>
-  <si>
-    <t>g_w89637370-400-w107937167-400</t>
-  </si>
-  <si>
-    <t>e_w90454383-400</t>
-  </si>
-  <si>
-    <t>g_w90454383-400-w169647963-400</t>
-  </si>
-  <si>
-    <t>g_w90454383-400-w89637370-400</t>
-  </si>
-  <si>
-    <t>g_w92348290-400-w102925909-400</t>
-  </si>
-  <si>
-    <t>g_w92348290-400-w200223220-400</t>
-  </si>
-  <si>
-    <t>g_w92348290-400-w98231311-400</t>
-  </si>
-  <si>
-    <t>e_w92348290-765</t>
-  </si>
-  <si>
-    <t>e_ZA28-765</t>
-  </si>
-  <si>
-    <t>g_w92348290-765-ZA28-765</t>
-  </si>
-  <si>
-    <t>g_w92348290-765-w167540668-765</t>
-  </si>
-  <si>
-    <t>g_w92348290-765-w193977981-765</t>
-  </si>
-  <si>
-    <t>g_w934819484-400-w167590549-400</t>
-  </si>
-  <si>
-    <t>e_w169789536-400</t>
-  </si>
-  <si>
-    <t>g_w934819484-400-w169789536-400</t>
-  </si>
-  <si>
-    <t>g_w98231311-400-w178968761-400</t>
+    <t>e_ZA11-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w220129604-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_ZA11-400_ZAF-w220129604-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_ZA15-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_ZA18-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_ZA15-400_ZAF-ZA18-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_ZA16-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_ZA18-400_ZAF-ZA16-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_ZA2-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w685294883-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_ZA2-400_ZAF-w685294883-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_ZA20-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_ZA20-400_ZAF-w220129604-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_ZA22-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w209976655-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_ZA22-400_ZAF-w209976655-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_ZA24-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w98231311-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_ZA24-400_ZAF-w98231311-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_ZA25-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w125769921-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_ZA25-400_ZAF-w125769921-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_ZA26-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w127585817-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_ZA26-400_ZAF-w127585817-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w213181313-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_ZA26-400_ZAF-w213181313-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_ZA29-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_ZA29-400_ZAF-w127585817-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_ZA3-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w200232961-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_ZA3-400_ZAF-w200232961-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_ZA30-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_ZA30-400_ZAF-ZA29-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w181284049-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_ZA30-400_ZAF-w181284049-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_ZA31-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w176362710-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_ZA31-400_ZAF-w176362710-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_ZA36-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_ZA36-400_ZAF-w176362710-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_ZA39-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w586032034-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_ZA39-400_ZAF-w586032034-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_ZA40-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w182042518-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_ZA40-400_ZAF-w182042518-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_ZA5-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_ZA4-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_ZA5-400_ZAF-ZA4-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_ZA6-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_ZA6-400_ZAF-ZA5-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_r17287657-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w631673098-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_r17287657-400_ZAF-w631673098-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w102682082-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w177800991-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w102682082-400_ZAF-w177800991-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w102925909-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w102925909-400_ZAF-w98231311-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w103079596-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w167540668-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w103079596-400_ZAF-w167540668-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w87404898-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w103079596-400_ZAF-w87404898-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w104080393-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w183759046-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w104080393-400_ZAF-w183759046-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w238322344-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w104080393-400_ZAF-w238322344-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w105759402-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w105759402-400_ZAF-w127585817-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w167648085-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w105759402-400_ZAF-w167648085-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w105811523-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w65600948-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w105811523-400_ZAF-w65600948-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w105811523-400_ZAF-w98231311-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w107431792-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w107431792-400_ZAF-ZA40-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w193978748-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w107431792-400_ZAF-w193978748-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w107937167-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w107937167-400_ZAF-r17287657-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w1146812331-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w1146878078-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w1146812331-400_ZAF-w1146878078-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w120584910-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w545652232-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w120584910-400_ZAF-w545652232-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w62191005-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w120584910-400_ZAF-w62191005-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w120941269-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w131625968-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w120941269-400_ZAF-w131625968-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w125754107-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w125754107-400_ZAF-w125769921-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w183402339-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w125769921-400_ZAF-w183402339-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w663042849-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w125769921-400_ZAF-w663042849-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w127585817-400_ZAF-ZA30-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_ZA33-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w127585817-400_ZAF-ZA33-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w127585817-400_ZAF-w176362710-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w142414070-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w181366662-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w142414070-400_ZAF-w181366662-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w89637370-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w142414070-400_ZAF-w89637370-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w92348290-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w142414070-400_ZAF-w92348290-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w142414070-765_ZAF</t>
+  </si>
+  <si>
+    <t>e_ZA38-765_ZAF</t>
+  </si>
+  <si>
+    <t>g_w142414070-765_ZAF-ZA38-765_ZAF</t>
+  </si>
+  <si>
+    <t>e_w181366662-765_ZAF</t>
+  </si>
+  <si>
+    <t>g_w142414070-765_ZAF-w181366662-765_ZAF</t>
+  </si>
+  <si>
+    <t>e_w156418705-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w184552955-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w156418705-400_ZAF-w184552955-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w162871098-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w162871098-400_ZAF-w125769921-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w87434264-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w167540668-400_ZAF-w87434264-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w167540668-765_ZAF</t>
+  </si>
+  <si>
+    <t>e_w178968761-765_ZAF</t>
+  </si>
+  <si>
+    <t>g_w167540668-765_ZAF-w178968761-765_ZAF</t>
+  </si>
+  <si>
+    <t>e_w167590549-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w167590549-400_ZAF-w142414070-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w167590549-400_ZAF-w177800991-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w167590549-400_ZAF-w62191005-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w89173873-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w167590549-400_ZAF-w89173873-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w167648085-400_ZAF-w120941269-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w167648085-400_ZAF-w181284049-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w219596295-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w167648085-400_ZAF-w219596295-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w169647963-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w169647963-400_ZAF-w89637370-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w170672051-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w170672051-400_ZAF-ZA15-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w185171518-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w170672051-400_ZAF-w185171518-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w170672051-400_ZAF-w209976655-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w170672051-400_ZAF-w220129604-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w107391770-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w176362710-400_ZAF-w107391770-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w207991752-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w176362710-400_ZAF-w207991752-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w176940672-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w184581460-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w176940672-400_ZAF-w184581460-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w934819484-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w177800991-400_ZAF-w934819484-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w178240552-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w178240552-400_ZAF-w105811523-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w178968761-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w178968761-400_ZAF-ZA22-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w185497473-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w178968761-400_ZAF-w185497473-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w209365700-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w178968761-400_ZAF-w209365700-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w178968761-400_ZAF-w238322344-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w178968761-400_ZAF-w65600948-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w179136373-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w179136373-400_ZAF-w213181313-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w179140081-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w179140081-400_ZAF-ZA22-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w179140081-400_ZAF-w178968761-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w179140081-400_ZAF-w209365700-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w181284049-400_ZAF-w107391770-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w181366662-400_ZAF-w107937167-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w181366662-400_ZAF-w92348290-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w179136373-765_ZAF</t>
+  </si>
+  <si>
+    <t>g_w181366662-765_ZAF-w179136373-765_ZAF</t>
+  </si>
+  <si>
+    <t>e_w219384657-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w182042518-400_ZAF-w219384657-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w182408147-400_ZAF-w184552955-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w182408147-400_ZAF-w685294883-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w183402339-400_ZAF-w142414070-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w183757901-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w183757901-400_ZAF-w219596295-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w183759046-400_ZAF-w167648085-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w184201271-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w184201271-400_ZAF-w176940672-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w184201271-400_ZAF-w200232961-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w184552955-400_ZAF-ZA6-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w208749745-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w184552955-400_ZAF-w208749745-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w184560833-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_ZA7-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w184560833-400_ZAF-ZA7-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w184560833-400_ZAF-w1146878078-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w83525879-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w184581460-400_ZAF-w83525879-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w185171518-400_ZAF-ZA15-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_ZA17-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w185171518-400_ZAF-ZA17-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w185171518-400_ZAF-w1146878078-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w185497473-400_ZAF-w170672051-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w185497473-400_ZAF-w178968761-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w193465369-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w193465369-400_ZAF-w193978748-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w193977981-765_ZAF</t>
+  </si>
+  <si>
+    <t>g_w193977981-765_ZAF-w142414070-765_ZAF</t>
+  </si>
+  <si>
+    <t>g_w193978748-400_ZAF-w125754107-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w200223220-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w200223220-400_ZAF-w98231311-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w200232961-400_ZAF-ZA2-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w200232961-400_ZAF-ZA3-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w200757306-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w496302277-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w200757306-400_ZAF-w496302277-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w209365700-400_ZAF-w167648085-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w209365700-400_ZAF-w179136373-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w209365700-400_ZAF-w213181313-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w209365700-400_ZAF-w238322344-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w209976655-400_ZAF-w220129604-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w260486370-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w209976655-400_ZAF-w260486370-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w213181313-400_ZAF-ZA29-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w213181313-400_ZAF-w167648085-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w213181313-400_ZAF-w219596295-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w219384657-400_ZAF-w62191005-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w219384657-765_ZAF</t>
+  </si>
+  <si>
+    <t>e_w586032034-765_ZAF</t>
+  </si>
+  <si>
+    <t>g_w219384657-765_ZAF-w586032034-765_ZAF</t>
+  </si>
+  <si>
+    <t>g_w219596295-400_ZAF-w120941269-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w219596295-400_ZAF-w131625968-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w220129604-400_ZAF-w156418705-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w230551819-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w230551819-400_ZAF-w176940672-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w230551819-400_ZAF-w182408147-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w230551819-400_ZAF-w184581460-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w230551819-400_ZAF-w200232961-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_ZA23-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w238322344-400_ZAF-ZA23-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w238322344-400_ZAF-w183757901-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w238322344-400_ZAF-w185171518-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w359805008-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w359805008-400_ZAF-ZA18-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w75136015-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w359805008-400_ZAF-w75136015-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w455498147-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w455498147-400_ZAF-w83525879-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w496302277-400_ZAF-w167540668-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w545652232-400_ZAF-w102682082-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w586032034-765_ZAF-w193977981-765_ZAF</t>
+  </si>
+  <si>
+    <t>g_w62191005-400_ZAF-w177800991-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w62193952-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w62193952-400_ZAF-w62191005-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w62218063-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w62218063-400_ZAF-w62193952-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w631673098-400_ZAF-w207991752-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w65600948-400_ZAF-w185171518-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w65600948-400_ZAF-w98231311-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w663042845-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w663042845-400_ZAF-w663042849-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w663042849-400_ZAF-w200757306-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w685294883-400_ZAF-ZA5-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w685294883-400_ZAF-w184552955-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w693869805-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w693869805-400_ZAF-ZA3-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w693869805-400_ZAF-w182408147-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w693869805-400_ZAF-w184201271-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w693869805-400_ZAF-w87434264-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w75136015-400_ZAF-ZA18-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w75136015-400_ZAF-w185497473-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w75136015-400_ZAF-w455498147-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w75136015-400_ZAF-w83525879-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_ZA14-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w83525879-400_ZAF-ZA14-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_ZA19-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w83525879-400_ZAF-ZA19-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w83525879-400_ZAF-w170672051-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w83525879-400_ZAF-w185497473-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w836844162-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w836844162-400_ZAF-ZA40-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_ZA41-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w836844162-400_ZAF-ZA41-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_ZA42-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w836844162-400_ZAF-ZA42-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_ZA43-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w836844162-400_ZAF-ZA43-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_ZA44-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w836844162-400_ZAF-ZA44-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w87404898-400_ZAF-w182408147-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w87404898-400_ZAF-w359805008-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w87404898-400_ZAF-w75136015-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w87404898-400_ZAF-w87434264-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w87434264-400_ZAF-w178240552-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w89173873-400_ZAF-w142414070-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w89173873-400_ZAF-w167590549-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w89637370-400_ZAF-w107937167-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w90454383-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w90454383-400_ZAF-w169647963-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w90454383-400_ZAF-w89637370-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w92348290-400_ZAF-w102925909-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w92348290-400_ZAF-w200223220-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w92348290-400_ZAF-w98231311-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w92348290-765_ZAF</t>
+  </si>
+  <si>
+    <t>e_ZA28-765_ZAF</t>
+  </si>
+  <si>
+    <t>g_w92348290-765_ZAF-ZA28-765_ZAF</t>
+  </si>
+  <si>
+    <t>g_w92348290-765_ZAF-w167540668-765_ZAF</t>
+  </si>
+  <si>
+    <t>g_w92348290-765_ZAF-w193977981-765_ZAF</t>
+  </si>
+  <si>
+    <t>g_w934819484-400_ZAF-w167590549-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w169789536-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w934819484-400_ZAF-w169789536-400_ZAF</t>
+  </si>
+  <si>
+    <t>g_w98231311-400_ZAF-w178968761-400_ZAF</t>
   </si>
   <si>
     <t>~tradelinks_desc</t>
@@ -1804,7 +1807,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D7269B6-F3DA-4019-BB78-37247926BE14}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6BE45E82-ECD8-45F8-9F6D-0A0AFE021827}">
   <dimension ref="B3:L186"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ZAF_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_ZAF_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ZAF_grids_kan\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2F400CFE-FBAF-45A0-82F2-EDEC77A155E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A16C1474-D124-4161-9756-D880E0F88070}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{C75B7F9D-5AB2-4223-87C5-D1E1EA2AC3ED}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{22788CD2-3136-4C69-A448-CFE54DBE8995}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -1807,7 +1807,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6BE45E82-ECD8-45F8-9F6D-0A0AFE021827}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{480B30E3-F535-4301-80E0-C0B7BEB4F713}">
   <dimension ref="B3:L186"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ZAF_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_ZAF_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ZAF_grids_kan\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A16C1474-D124-4161-9756-D880E0F88070}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E2D8417E-8402-4C10-B9E5-24AFD7FDB730}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{22788CD2-3136-4C69-A448-CFE54DBE8995}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{7A12C204-5C6A-4315-BF9E-A05ED6EBDF27}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -1807,7 +1807,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{480B30E3-F535-4301-80E0-C0B7BEB4F713}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4ED5188-4281-4DCE-B0C4-B9A2D805373A}">
   <dimension ref="B3:L186"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ZAF_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_ZAF_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ZAF_grids_kan\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E2D8417E-8402-4C10-B9E5-24AFD7FDB730}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{67361DB0-D2A4-4C29-AED4-12A3E23C87AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{7A12C204-5C6A-4315-BF9E-A05ED6EBDF27}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{D1904D03-A684-4E0C-AB0E-AF4C27DAC535}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -1807,7 +1807,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4ED5188-4281-4DCE-B0C4-B9A2D805373A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2624913-A75A-4725-BA2C-B301D92CBF23}">
   <dimension ref="B3:L186"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ZAF_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_ZAF_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ZAF_grids_kan\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{67361DB0-D2A4-4C29-AED4-12A3E23C87AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{911BAD6E-BD89-4EC7-9179-CA4A2DFFD5C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{D1904D03-A684-4E0C-AB0E-AF4C27DAC535}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{15BB3AF4-C209-4702-9522-07B53688806B}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -1807,7 +1807,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2624913-A75A-4725-BA2C-B301D92CBF23}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D10576C2-DC0B-405F-945C-A5CB5CB960AC}">
   <dimension ref="B3:L186"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ZAF_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_ZAF_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ZAF_grids_kan\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{911BAD6E-BD89-4EC7-9179-CA4A2DFFD5C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2B548208-4989-491F-A732-E26C4D483334}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{15BB3AF4-C209-4702-9522-07B53688806B}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{5EEC5798-1D57-4AA3-A678-FC652412ED88}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -1807,7 +1807,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D10576C2-DC0B-405F-945C-A5CB5CB960AC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7CA705B6-C049-4643-84D8-4DC68456989C}">
   <dimension ref="B3:L186"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ZAF_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_ZAF_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ZAF_grids_kan\SuppXLS\trades\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_ZAF_grids_kan\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2B548208-4989-491F-A732-E26C4D483334}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E2C3FC3-0EF5-4770-A9AE-DEC62EA7D5E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{5EEC5798-1D57-4AA3-A678-FC652412ED88}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{D1904D03-A684-4E0C-AB0E-AF4C27DAC535}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -1807,9 +1807,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7CA705B6-C049-4643-84D8-4DC68456989C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2624913-A75A-4725-BA2C-B301D92CBF23}">
   <dimension ref="B3:L186"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="2" max="2" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.1328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.73046875" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="21.19921875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="40.53125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.59765625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="40.53125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="38.19921875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="3" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B3" t="s">
